--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128549967</v>
       </c>
       <c r="B3" t="n">
-        <v>57771</v>
+        <v>57775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128549967</v>
       </c>
       <c r="B3" t="n">
-        <v>57775</v>
+        <v>57802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128549967</v>
       </c>
       <c r="B3" t="n">
-        <v>57802</v>
+        <v>57806</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>128549967</v>
       </c>
       <c r="B3" t="n">
-        <v>57806</v>
+        <v>57809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549959</v>
       </c>
       <c r="B2" t="n">
-        <v>9173</v>
+        <v>9178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128549967</v>
+        <v>128549958</v>
       </c>
       <c r="B3" t="n">
-        <v>57809</v>
+        <v>7166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102626</v>
+        <v>101783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Tvåtandad plattbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Silvanus bidentatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584341</v>
+        <v>584328</v>
       </c>
       <c r="R3" t="n">
-        <v>6318617</v>
+        <v>6318709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>06:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128549958</v>
+        <v>128549973</v>
       </c>
       <c r="B4" t="n">
-        <v>7163</v>
+        <v>45045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101783</v>
+        <v>102019</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåtandad plattbagge</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silvanus bidentatus</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584328</v>
+        <v>584284</v>
       </c>
       <c r="R4" t="n">
-        <v>6318709</v>
+        <v>6318697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>06:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,32 +1023,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128549971</v>
+        <v>128549967</v>
       </c>
       <c r="B5" t="n">
-        <v>5027</v>
+        <v>58039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101608</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584329</v>
+        <v>584341</v>
       </c>
       <c r="R5" t="n">
-        <v>6318707</v>
+        <v>6318617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 43774-2021 artfynd.xlsx
+++ b/artfynd/A 43774-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549958</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>